--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.0.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.1.</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2080,7 +2080,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T20:02:16+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T20:16:06+00:00. Normalization version: v1.1.</t>
         </is>
       </c>
     </row>
@@ -2097,14 +2097,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx       — country aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx        — country aggregates</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx   — market aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx    — market aggregates</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_COMPSETS.xlsx   — compset (peer-set) benchmarks per target hotel</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx       — chain-scale time series (country or market level)</t>
         </is>
       </c>
     </row>
@@ -2128,147 +2128,164 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operating contract:</t>
+          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
+          <t xml:space="preserve">  (different purpose — hotel-specific underwriting outputs, not warehouse ingestion).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+          <t>Operating contract:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">     in ingested_by + notes.</t>
+          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sheets:</t>
+          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
+          <t xml:space="preserve">     in ingested_by + notes.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+          <t>Sheets:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • README            — this sheet</t>
+          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reference docs:</t>
+          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-country-schema.md</t>
+          <t xml:space="preserve">  • README            — this sheet</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+          <t>Reference docs:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-country-schema.md</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Regenerating this workbook:</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regenerating this workbook:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Idempotent. Run when the schema evolves; commit both the script and the regenerated .xlsx.)</t>
         </is>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -450,17 +450,17 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -470,12 +470,12 @@
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
     <col width="23" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="17" customWidth="1" min="35" max="35"/>
@@ -681,6 +681,4120 @@
           <t>notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>75.11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>164.1423</v>
+      </c>
+      <c r="I2" t="n">
+        <v>123.2931</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="S2" t="n">
+        <v>941917</v>
+      </c>
+      <c r="T2" t="n">
+        <v>18453</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="H3" t="n">
+        <v>116.5024</v>
+      </c>
+      <c r="I3" t="n">
+        <v>78.32250000000001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.5499999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>781640</v>
+      </c>
+      <c r="T3" t="n">
+        <v>20825</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>77.41</v>
+      </c>
+      <c r="H4" t="n">
+        <v>139.758938805228</v>
+      </c>
+      <c r="I4" t="n">
+        <v>108.191856143792</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>722052</v>
+      </c>
+      <c r="T4" t="n">
+        <v>17635</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="H5" t="n">
+        <v>175.4577</v>
+      </c>
+      <c r="I5" t="n">
+        <v>113.8605</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="S5" t="n">
+        <v>653264</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8825</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="H6" t="n">
+        <v>223.8694</v>
+      </c>
+      <c r="I6" t="n">
+        <v>155.3078</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>488265</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6325</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>277.7348</v>
+      </c>
+      <c r="I7" t="n">
+        <v>194.6806</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>289894</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3884</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>100.345129768242</v>
+      </c>
+      <c r="I8" t="n">
+        <v>68.34169512816641</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P8" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="S8" t="n">
+        <v>185366</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9488</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="H9" t="n">
+        <v>113.61758899866</v>
+      </c>
+      <c r="I9" t="n">
+        <v>73.7626272724832</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="P9" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="S9" t="n">
+        <v>183660</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1616</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>70.58</v>
+      </c>
+      <c r="H10" t="n">
+        <v>143.1859</v>
+      </c>
+      <c r="I10" t="n">
+        <v>101.0627</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.850000000000001</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.260000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>164173</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3388</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>163.9112</v>
+      </c>
+      <c r="I11" t="n">
+        <v>111.0263</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>154304</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7490</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>65.60000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>269.878038771593</v>
+      </c>
+      <c r="I12" t="n">
+        <v>177.025981957773</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S12" t="n">
+        <v>137068</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1289</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="H13" t="n">
+        <v>92.35015477104599</v>
+      </c>
+      <c r="I13" t="n">
+        <v>64.1360753347692</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="S13" t="n">
+        <v>136184</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9983</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>54.29000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>101.413954263355</v>
+      </c>
+      <c r="I14" t="n">
+        <v>55.0566388348459</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>82432</v>
+      </c>
+      <c r="T14" t="n">
+        <v>541</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="H15" t="n">
+        <v>119.258278603363</v>
+      </c>
+      <c r="I15" t="n">
+        <v>74.56026564677541</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="S15" t="n">
+        <v>82309</v>
+      </c>
+      <c r="T15" t="n">
+        <v>381</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>58.04000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>90.9948251082678</v>
+      </c>
+      <c r="I16" t="n">
+        <v>52.8119339950093</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="P16" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="S16" t="n">
+        <v>80939</v>
+      </c>
+      <c r="T16" t="n">
+        <v>813</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>175.0613</v>
+      </c>
+      <c r="I17" t="n">
+        <v>98.8783</v>
+      </c>
+      <c r="O17" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S17" t="n">
+        <v>75874</v>
+      </c>
+      <c r="T17" t="n">
+        <v>562</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>113.63855951474</v>
+      </c>
+      <c r="I18" t="n">
+        <v>81.5948490399165</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="S18" t="n">
+        <v>67643</v>
+      </c>
+      <c r="T18" t="n">
+        <v>667</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="H19" t="n">
+        <v>153.344834286982</v>
+      </c>
+      <c r="I19" t="n">
+        <v>92.6111129435407</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>66065</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2674</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>70.00999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>134.9106</v>
+      </c>
+      <c r="I20" t="n">
+        <v>94.4558</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>64894</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1448</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="H21" t="n">
+        <v>119.31090313757</v>
+      </c>
+      <c r="I21" t="n">
+        <v>85.76771275199491</v>
+      </c>
+      <c r="O21" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>59062</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2150</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>63.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>91.14767600470201</v>
+      </c>
+      <c r="I22" t="n">
+        <v>57.8353850615406</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="S22" t="n">
+        <v>45522</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2295</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="H23" t="n">
+        <v>90.7131707522757</v>
+      </c>
+      <c r="I23" t="n">
+        <v>38.6099368007303</v>
+      </c>
+      <c r="O23" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="P23" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="S23" t="n">
+        <v>29544</v>
+      </c>
+      <c r="T23" t="n">
+        <v>310</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="H24" t="n">
+        <v>173.0838</v>
+      </c>
+      <c r="I24" t="n">
+        <v>124.1304</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="S24" t="n">
+        <v>23697</v>
+      </c>
+      <c r="T24" t="n">
+        <v>828</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="H25" t="n">
+        <v>107.0898</v>
+      </c>
+      <c r="I25" t="n">
+        <v>65.80759999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="S25" t="n">
+        <v>19088</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="H26" t="n">
+        <v>118.0414</v>
+      </c>
+      <c r="I26" t="n">
+        <v>82.2402</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15643</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>63.18</v>
+      </c>
+      <c r="H27" t="n">
+        <v>134.362334584526</v>
+      </c>
+      <c r="I27" t="n">
+        <v>84.88332071648129</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-6.660000000000001</v>
+      </c>
+      <c r="P27" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S27" t="n">
+        <v>14418</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1128</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="H28" t="n">
+        <v>110.717731806527</v>
+      </c>
+      <c r="I28" t="n">
+        <v>58.1361068971847</v>
+      </c>
+      <c r="O28" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="S28" t="n">
+        <v>13201</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1626</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>123.6019</v>
+      </c>
+      <c r="I29" t="n">
+        <v>59.5517</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11988</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>55.38999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>221.2097</v>
+      </c>
+      <c r="I30" t="n">
+        <v>122.5346</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9359</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1446</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="H31" t="n">
+        <v>146.2117</v>
+      </c>
+      <c r="I31" t="n">
+        <v>105.3196</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6729</v>
+      </c>
+      <c r="T31" t="n">
+        <v>219</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>130.72381779037</v>
+      </c>
+      <c r="I32" t="n">
+        <v>73.3868079542016</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="P32" t="n">
+        <v>7.290000000000001</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6187</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1773</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>6113</v>
+      </c>
+      <c r="T33" t="n">
+        <v>262</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="H34" t="n">
+        <v>101.537454051629</v>
+      </c>
+      <c r="I34" t="n">
+        <v>46.7405002050437</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4110</v>
+      </c>
+      <c r="T34" t="n">
+        <v>215</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>64.05999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>592.3021</v>
+      </c>
+      <c r="I35" t="n">
+        <v>379.4082</v>
+      </c>
+      <c r="O35" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2434</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>1251</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>1056</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>739</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>705</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>640</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>603</v>
+      </c>
+      <c r="T41" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>504</v>
+      </c>
+      <c r="T42" t="n">
+        <v>230</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>499</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>458</v>
+      </c>
+      <c r="T44" t="n">
+        <v>198</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>96</v>
+      </c>
+      <c r="T45" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1617,7 +5731,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.1.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2054,7 +6168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2080,7 +6194,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T20:16:06+00:00. Normalization version: v1.1.</t>
+          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2097,195 +6211,202 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx        — country aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx                  — country aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx    — market aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx              — market aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_SUBMERCADOS.xlsx — submarket aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_SUBMERCADOS.xlsx           — submarket aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx       — chain-scale time series (country or market level)</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_HOTELES_POR_MERCADO.xlsx   — hotel inventory (Dataset B · v1.2)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx                 — LEGACY (chain-scale aggregates · retired v1.2)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t xml:space="preserve">  (different purpose — hotel-specific underwriting outputs, not warehouse ingestion).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Operating contract:</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
+          <t>Operating contract:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
+          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">     in ingested_by + notes.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sheets:</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
+          <t>Sheets:</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
+          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • README            — this sheet</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Reference docs:</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-country-schema.md</t>
+          <t>Reference docs:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-country-schema.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Regenerating this workbook:</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
+          <t>Regenerating this workbook:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Idempotent. Run when the schema evolves; commit both the script and the regenerated .xlsx.)</t>
         </is>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -752,7 +752,7 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -850,7 +850,7 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -948,7 +948,7 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1144,7 +1144,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1242,7 +1242,7 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1340,7 +1340,7 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1438,7 +1438,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1536,7 +1536,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1634,7 +1634,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1732,7 +1732,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -1830,7 +1830,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2026,7 +2026,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2124,7 +2124,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2222,7 +2222,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2320,7 +2320,7 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2418,7 +2418,7 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2516,7 +2516,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -2614,7 +2614,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -2712,7 +2712,7 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -2908,7 +2908,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3006,7 +3006,7 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3104,7 +3104,7 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3202,7 +3202,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3300,7 +3300,7 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -3398,7 +3398,7 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -3496,7 +3496,7 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -3692,7 +3692,7 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -3772,7 +3772,7 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -3870,7 +3870,7 @@
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -3968,7 +3968,7 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4048,7 +4048,7 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -4128,7 +4128,7 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -4208,7 +4208,7 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -4288,7 +4288,7 @@
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -4368,7 +4368,7 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -4448,7 +4448,7 @@
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -4608,7 +4608,7 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -4688,7 +4688,7 @@
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -4768,7 +4768,7 @@
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6194,7 +6194,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM45"/>
+  <dimension ref="A1:AO45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,20 +469,22 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="24" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="19" customWidth="1" min="32" max="32"/>
-    <col width="23" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="17" customWidth="1" min="35" max="35"/>
-    <col width="15" customWidth="1" min="36" max="36"/>
-    <col width="18" customWidth="1" min="37" max="37"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="19" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="15" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -613,70 +615,80 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>rooms_under_construction</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>rooms_delivered_12m</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>canonical_id</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ingestion_id</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>source_kind</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ingested_at</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>ingested_by</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>normalization_version</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dedup_key</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>review_required</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>review_reason</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ingestion_status</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>supersedes_id</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -729,56 +741,62 @@
       <c r="T2" t="n">
         <v>18453</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z2" t="n">
+        <v>18453</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6042</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -827,56 +845,62 @@
       <c r="T3" t="n">
         <v>20825</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z3" t="n">
+        <v>20825</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7298</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -925,56 +949,62 @@
       <c r="T4" t="n">
         <v>17635</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z4" t="n">
+        <v>17635</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6022</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1023,56 +1053,62 @@
       <c r="T5" t="n">
         <v>8825</v>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z5" t="n">
+        <v>8825</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4357</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1121,56 +1157,62 @@
       <c r="T6" t="n">
         <v>6325</v>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z6" t="n">
+        <v>6325</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3802</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1219,56 +1261,62 @@
       <c r="T7" t="n">
         <v>3884</v>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z7" t="n">
+        <v>3884</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1553</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1317,56 +1365,62 @@
       <c r="T8" t="n">
         <v>9488</v>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z8" t="n">
+        <v>9488</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1947</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1415,56 +1469,62 @@
       <c r="T9" t="n">
         <v>1616</v>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z9" t="n">
+        <v>1616</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1513,56 +1573,62 @@
       <c r="T10" t="n">
         <v>3388</v>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z10" t="n">
+        <v>3388</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1275</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1611,56 +1677,62 @@
       <c r="T11" t="n">
         <v>7490</v>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z11" t="n">
+        <v>7490</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3104</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1709,56 +1781,62 @@
       <c r="T12" t="n">
         <v>1289</v>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z12" t="n">
+        <v>1289</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>441</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1807,56 +1885,62 @@
       <c r="T13" t="n">
         <v>9983</v>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z13" t="n">
+        <v>9983</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2900</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1905,56 +1989,62 @@
       <c r="T14" t="n">
         <v>541</v>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z14" t="n">
+        <v>541</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2003,56 +2093,62 @@
       <c r="T15" t="n">
         <v>381</v>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z15" t="n">
+        <v>381</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>305</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2101,56 +2197,62 @@
       <c r="T16" t="n">
         <v>813</v>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z16" t="n">
+        <v>813</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2199,56 +2301,62 @@
       <c r="T17" t="n">
         <v>562</v>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z17" t="n">
+        <v>562</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>594</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2297,56 +2405,62 @@
       <c r="T18" t="n">
         <v>667</v>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z18" t="n">
+        <v>667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>158</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2395,56 +2509,62 @@
       <c r="T19" t="n">
         <v>2674</v>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z19" t="n">
+        <v>2674</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>480</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2493,56 +2613,62 @@
       <c r="T20" t="n">
         <v>1448</v>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z20" t="n">
+        <v>1448</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1431</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2591,56 +2717,62 @@
       <c r="T21" t="n">
         <v>2150</v>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z21" t="n">
+        <v>2150</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>556</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2689,56 +2821,62 @@
       <c r="T22" t="n">
         <v>2295</v>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z22" t="n">
+        <v>2295</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>184</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AI22" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2787,56 +2925,62 @@
       <c r="T23" t="n">
         <v>310</v>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z23" t="n">
+        <v>310</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>73</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2885,56 +3029,62 @@
       <c r="T24" t="n">
         <v>828</v>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z24" t="n">
+        <v>828</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>940</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AI24" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2983,56 +3133,62 @@
       <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>39</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3081,56 +3237,62 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3179,56 +3341,62 @@
       <c r="T27" t="n">
         <v>1128</v>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z27" t="n">
+        <v>1128</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>96</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3277,56 +3445,62 @@
       <c r="T28" t="n">
         <v>1626</v>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z28" t="n">
+        <v>1626</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3375,56 +3549,62 @@
       <c r="T29" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>17</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3473,56 +3653,62 @@
       <c r="T30" t="n">
         <v>1446</v>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z30" t="n">
+        <v>1446</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>240</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3571,56 +3757,62 @@
       <c r="T31" t="n">
         <v>219</v>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z31" t="n">
+        <v>219</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>283</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3669,56 +3861,62 @@
       <c r="T32" t="n">
         <v>1773</v>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z32" t="n">
+        <v>1773</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>208</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3749,56 +3947,62 @@
       <c r="T33" t="n">
         <v>262</v>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z33" t="n">
+        <v>262</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3847,56 +4051,62 @@
       <c r="T34" t="n">
         <v>215</v>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z34" t="n">
+        <v>215</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3945,56 +4155,62 @@
       <c r="T35" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4025,56 +4241,62 @@
       <c r="T36" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4105,56 +4327,62 @@
       <c r="T37" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4185,56 +4413,62 @@
       <c r="T38" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr">
+      <c r="AI38" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4265,56 +4499,62 @@
       <c r="T39" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>126</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4345,56 +4585,62 @@
       <c r="T40" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG40" t="inlineStr">
+      <c r="AI40" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4425,56 +4671,62 @@
       <c r="T41" t="n">
         <v>120</v>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z41" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AI41" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4505,56 +4757,62 @@
       <c r="T42" t="n">
         <v>230</v>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z42" t="n">
+        <v>230</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AE42" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr">
+      <c r="AI42" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4585,56 +4843,62 @@
       <c r="T43" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AE43" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr">
+      <c r="AI43" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4665,56 +4929,62 @@
       <c r="T44" t="n">
         <v>198</v>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z44" t="n">
+        <v>198</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>120</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AE44" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG44" t="inlineStr">
+      <c r="AI44" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4745,56 +5015,62 @@
       <c r="T45" t="n">
         <v>200</v>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
+      <c r="Z45" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>32</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AE45" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AI45" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4807,7 +5083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5522,54 +5798,54 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ingestion_meta</t>
+          <t>domain</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>canonical_id</t>
+          <t>rooms_under_construction</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Primary key in the master. Generated on first insertion. Stable across edits.</t>
+          <t>Rooms under construction — 'Habitaciones construcción'.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ingestion_meta</t>
+          <t>domain</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ingestion_id</t>
+          <t>rooms_delivered_12m</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Matches the ingestion log entry that landed this row.</t>
+          <t>Rooms delivered last 12 months — 'Habitaciones entregadas 12 m.'.</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5857,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>source_file</t>
+          <t>canonical_id</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5596,7 +5872,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Original filename verbatim — e.g. 'CoStar_ES_Country_2026Q1.xlsx'.</t>
+          <t>Primary key in the master. Generated on first insertion. Stable across edits.</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5884,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>source_kind</t>
+          <t>ingestion_id</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -5623,7 +5899,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>costar | str | kalibri | curated | manual</t>
+          <t>Matches the ingestion log entry that landed this row.</t>
         </is>
       </c>
     </row>
@@ -5635,22 +5911,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>source_file</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Public URL when applicable.</t>
+          <t>Original filename verbatim — e.g. 'CoStar_ES_Country_2026Q1.xlsx'.</t>
         </is>
       </c>
     </row>
@@ -5662,12 +5938,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ingested_at</t>
+          <t>source_kind</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5677,7 +5953,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ISO-8601 UTC. Auto-stamped by the ingestion run.</t>
+          <t>costar | str | kalibri | curated | manual</t>
         </is>
       </c>
     </row>
@@ -5689,22 +5965,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ingested_by</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Operator email — audit trail.</t>
+          <t>Public URL when applicable.</t>
         </is>
       </c>
     </row>
@@ -5716,12 +5992,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>normalization_version</t>
+          <t>ingested_at</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5731,7 +6007,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
+          <t>ISO-8601 UTC. Auto-stamped by the ingestion run.</t>
         </is>
       </c>
     </row>
@@ -5743,12 +6019,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>dedup_key</t>
+          <t>ingested_by</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -5758,7 +6034,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sha256 of the canonicalised dedup fields (see costar-normalization-rules.md §4).</t>
+          <t>Operator email — audit trail.</t>
         </is>
       </c>
     </row>
@@ -5770,12 +6046,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>normalization_version</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5785,7 +6061,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>TRUE when validation flagged something.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
         </is>
       </c>
     </row>
@@ -5797,7 +6073,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>review_reason</t>
+          <t>dedup_key</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -5807,12 +6083,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Short label — e.g. 'missing_period', 'duplicate_candidate', 'fx_conversion_applied'.</t>
+          <t>sha256 of the canonicalised dedup fields (see costar-normalization-rules.md §4).</t>
         </is>
       </c>
     </row>
@@ -5824,12 +6100,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ingestion_status</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5839,7 +6115,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ingested | under_review | superseded | rejected</t>
+          <t>TRUE when validation flagged something.</t>
         </is>
       </c>
     </row>
@@ -5851,12 +6127,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>supersedes_id</t>
+          <t>review_reason</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5866,7 +6142,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Set when this row corrects/replaces a previously canonical row.</t>
+          <t>Short label — e.g. 'missing_period', 'duplicate_candidate', 'fx_conversion_applied'.</t>
         </is>
       </c>
     </row>
@@ -5878,20 +6154,74 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
+          <t>ingestion_status</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ingested | under_review | superseded | rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ingestion_meta</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>supersedes_id</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Set when this row corrects/replaces a previously canonical row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ingestion_meta</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Free-form operator notes.</t>
         </is>
@@ -6194,7 +6524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -770,7 +770,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -874,7 +874,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2538,7 +2538,7 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -3578,7 +3578,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4184,7 +4184,7 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -4700,7 +4700,7 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -4872,7 +4872,7 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -770,7 +770,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -874,7 +874,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2538,7 +2538,7 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -3578,7 +3578,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4184,7 +4184,7 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -4700,7 +4700,7 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -4872,7 +4872,7 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:23:25+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -770,7 +770,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -874,7 +874,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2538,7 +2538,7 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -3578,7 +3578,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4184,7 +4184,7 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -4700,7 +4700,7 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -4872,7 +4872,7 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:23:25+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -770,7 +770,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -874,7 +874,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2538,7 +2538,7 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -3578,7 +3578,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4184,7 +4184,7 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -4700,7 +4700,7 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -4872,7 +4872,7 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_PAIS.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -770,7 +770,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -874,7 +874,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1810,7 +1810,7 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2018,7 +2018,7 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -2538,7 +2538,7 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -2746,7 +2746,7 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -3578,7 +3578,7 @@
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -3786,7 +3786,7 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -3890,7 +3890,7 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -3976,7 +3976,7 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4184,7 +4184,7 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4270,7 +4270,7 @@
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -4356,7 +4356,7 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -4528,7 +4528,7 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -4700,7 +4700,7 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -4872,7 +4872,7 @@
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -6524,7 +6524,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:48:39+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
